--- a/artfynd/S 1328-2022 artfynd.xlsx
+++ b/artfynd/S 1328-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96201749</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96201761</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124556813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124556815</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1220,6 +1245,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647641</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647643</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647644</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647645</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647637</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647638</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647655</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1951,6 +2011,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647656</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067951</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,6 +2239,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/431004</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2272,6 +2347,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067908</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2375,6 +2455,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067909</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067910</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2563,6 +2653,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067911</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2660,6 +2755,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647587</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2757,6 +2857,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647588</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2854,6 +2959,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647589</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2951,6 +3061,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647590</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3048,6 +3163,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647597</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3145,6 +3265,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647598</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,6 +3367,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647599</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3348,6 +3478,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067907</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3445,6 +3580,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647592</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3542,6 +3682,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647591</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,6 +3784,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647600</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3736,6 +3886,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647601</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3833,6 +3988,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647602</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3930,6 +4090,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647603</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4027,6 +4192,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647605</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4133,6 +4303,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647616</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4239,6 +4414,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647617</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4345,6 +4525,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647621</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4456,6 +4641,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647622</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4562,6 +4752,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067918</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4668,6 +4863,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067929</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4774,6 +4974,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067931</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4871,6 +5076,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647604</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4968,6 +5178,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647607</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5065,6 +5280,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647608</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5162,6 +5382,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647609</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5259,6 +5484,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123647610</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5356,6 +5586,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067900</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5453,6 +5688,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067901</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5550,6 +5790,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067902</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5647,6 +5892,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067903</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5749,6 +5999,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067904</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5851,8 +6106,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126067905</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>